--- a/_site/SourceDocuments/ResearchAroundTheWorld-Data.xlsx
+++ b/_site/SourceDocuments/ResearchAroundTheWorld-Data.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="50">
   <si>
     <t xml:space="preserve">Place</t>
   </si>
@@ -49,32 +49,7 @@
     <t xml:space="preserve">Research Associate</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Molecular and population genetics of farmed strains and wild populations of turbot and halibut. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Juvenile growth and social hierarchies of flatfish. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Courier New"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Oversaw a range of research projects covering various marine species e.g. turbot, halibut, trout, scallops.</t>
-    </r>
+    <t xml:space="preserve">Molecular and population genetics of farmed strains and wild populations of turbot and halibut. Juvenile growth and social hierarchies of flatfish. Oversaw a range of research projects covering various marine species e.g. turbot, halibut, trout, scallops.</t>
   </si>
   <si>
     <t xml:space="preserve">Marine and Freshwater Institute</t>
@@ -170,7 +145,16 @@
     <t xml:space="preserve">Consulting scientist on data analysis, natural resources, and sustainability.</t>
   </si>
   <si>
-    <t xml:space="preserve">Consulting scientist on fisheries, resource management, sustainability, and climate change.</t>
+    <t xml:space="preserve">Freymar LLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freymar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder &amp; General Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consulting scientist on fisheries, resource management, sustainability, bioprocessing, and climate change.</t>
   </si>
   <si>
     <t xml:space="preserve">University of Bergen</t>
@@ -196,7 +180,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -224,11 +208,6 @@
       <name val="Courier New"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Courier New"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -289,7 +268,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -297,7 +276,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -317,6 +296,112 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -328,7 +413,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="4.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="61.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="61.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -351,7 +436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="71.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -371,7 +456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="47.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -393,7 +478,7 @@
       </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="36.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="47.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -476,7 +561,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="47.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
@@ -494,7 +579,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="47.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
@@ -514,7 +599,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="59.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -534,7 +619,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="24.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -554,12 +639,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="24.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="36.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>42.091</v>
@@ -568,18 +653,18 @@
         <v>-72.083</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="36.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>60.381</v>
@@ -588,18 +673,18 @@
         <v>5.333</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="47.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>51.644</v>
@@ -611,7 +696,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
